--- a/marketing_report/outputs/Cursos/Analisis_CRM/16_Inscriptos_Sin_Lead.xlsx
+++ b/marketing_report/outputs/Cursos/Analisis_CRM/16_Inscriptos_Sin_Lead.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="224">
   <si>
     <t>Consulta: ID Consulta</t>
   </si>
@@ -349,6 +349,9 @@
     <t>00QTV00000VPpiE2AT</t>
   </si>
   <si>
+    <t>00QTV00000Tqli62AB</t>
+  </si>
+  <si>
     <t>00QTV00000Haz4q2AB</t>
   </si>
   <si>
@@ -361,6 +364,9 @@
     <t>gmlun2@gmail.com</t>
   </si>
   <si>
+    <t>melilagoria@gmail.com</t>
+  </si>
+  <si>
     <t>marihenderson@hotmail.com.ar</t>
   </si>
   <si>
@@ -373,6 +379,9 @@
     <t>Maxi Luna</t>
   </si>
   <si>
+    <t>Melina Lagoria</t>
+  </si>
+  <si>
     <t>Mariela Mariela</t>
   </si>
   <si>
@@ -391,9 +400,15 @@
     <t>Distancia</t>
   </si>
   <si>
+    <t>Presencial</t>
+  </si>
+  <si>
     <t>LICENCIATURA EN ENTRENAMIENTO DEPORTIVO - CICLO DE COMPLEMENTACIÓN CURRICULAR</t>
   </si>
   <si>
+    <t>LICENCIATURA EN RECURSOS HUMANOS</t>
+  </si>
+  <si>
     <t>TECNICATURA UNIVERSITARIA EN ORGANIZACIÓN Y DIRECCIÓN DE EVENTOS Y CEREMONIAL</t>
   </si>
   <si>
@@ -406,6 +421,9 @@
     <t>81- S.M DE TUCUMÁN</t>
   </si>
   <si>
+    <t>SALTA - CASTAÑARES PRESENCIAL</t>
+  </si>
+  <si>
     <t>DELEGACIÓN ROSARIO - SANTA FE</t>
   </si>
   <si>
@@ -445,15 +463,18 @@
     <t>Abierto</t>
   </si>
   <si>
+    <t>Interesado</t>
+  </si>
+  <si>
     <t>No interesado</t>
   </si>
   <si>
-    <t>Interesado</t>
-  </si>
-  <si>
     <t>19/2/2026</t>
   </si>
   <si>
+    <t>8/1/2026</t>
+  </si>
+  <si>
     <t>23/3/2025</t>
   </si>
   <si>
@@ -469,6 +490,9 @@
     <t>23/2/2026, 22:03</t>
   </si>
   <si>
+    <t>9/1/2026, 00:01</t>
+  </si>
+  <si>
     <t>UCASAL Prod</t>
   </si>
   <si>
@@ -481,15 +505,15 @@
     <t>Contact Center</t>
   </si>
   <si>
+    <t>Estefanía Pamela Quintana</t>
+  </si>
+  <si>
     <t>Daniel Luciano Chaile Soto</t>
   </si>
   <si>
     <t>SALTA - DISTANCIA</t>
   </si>
   <si>
-    <t>SALTA - CASTAÑARES PRESENCIAL</t>
-  </si>
-  <si>
     <t>FACULTAD DE EDUCACIÓN</t>
   </si>
   <si>
@@ -502,12 +526,12 @@
     <t>IA GENERATIVA PARA DOCENTES UNIVERSITARIOS: ENSEÑAR, APRENDER Y CREAR EN LA ERA DIGITAL</t>
   </si>
   <si>
+    <t>CURSO INTENSIVO DE INGLÉS</t>
+  </si>
+  <si>
     <t>CURSO DE CONVERSACIÓN EN INGLÉS</t>
   </si>
   <si>
-    <t>CURSO INTENSIVO DE INGLÉS</t>
-  </si>
-  <si>
     <t>DIPLOMATURA UNIVERSITARIA DE ULTRASONOGRAFÍA ABDOMINAL DIAGNÓSTICA EN PEQUEÑOS ANIMALES</t>
   </si>
   <si>
@@ -526,6 +550,9 @@
     <t>LUNA, PABLO FEDERICO MOISÉS</t>
   </si>
   <si>
+    <t>GIMENEZ LAGORIA , MARIA MICAELA</t>
+  </si>
+  <si>
     <t>CAPALDO, MARIELA ELSA</t>
   </si>
   <si>
@@ -538,6 +565,9 @@
     <t>pmluna@gmail.com</t>
   </si>
   <si>
+    <t>marilagoria@gmail.com</t>
+  </si>
+  <si>
     <t>marielacapaldo@gmail.com</t>
   </si>
   <si>
@@ -550,12 +580,18 @@
     <t>387 - 4206212</t>
   </si>
   <si>
+    <t>0 - 0000</t>
+  </si>
+  <si>
     <t xml:space="preserve">- </t>
   </si>
   <si>
     <t>387 - 5298537</t>
   </si>
   <si>
+    <t>387 - 4624817</t>
+  </si>
+  <si>
     <t>387 - 5607351</t>
   </si>
   <si>
@@ -577,6 +613,9 @@
     <t>2026-02-11</t>
   </si>
   <si>
+    <t>2026-02-04</t>
+  </si>
+  <si>
     <t>2026-02-03</t>
   </si>
   <si>
@@ -598,6 +637,9 @@
     <t>9-2241945,18501853</t>
   </si>
   <si>
+    <t>8-1961356,0</t>
+  </si>
+  <si>
     <t>8-1969009,0</t>
   </si>
   <si>
@@ -610,6 +652,9 @@
     <t>LUNA</t>
   </si>
   <si>
+    <t>GIMENEZ LAGORIA</t>
+  </si>
+  <si>
     <t>CAPALDO</t>
   </si>
   <si>
@@ -620,6 +665,9 @@
   </si>
   <si>
     <t>PABLO FEDERICO MOISÉS</t>
+  </si>
+  <si>
+    <t>MARIA MICAELA</t>
   </si>
   <si>
     <t>MARIELA ELSA</t>
@@ -995,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:DF5"/>
+  <dimension ref="A1:DF6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:110">
@@ -1338,64 +1386,64 @@
         <v>110</v>
       </c>
       <c r="C2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F2">
         <v>3815765777</v>
       </c>
       <c r="G2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I2">
         <v>186</v>
       </c>
       <c r="J2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K2">
         <v>81</v>
       </c>
       <c r="L2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="M2">
         <v>18</v>
       </c>
       <c r="S2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="T2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="U2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="V2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="W2" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="X2" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="Y2" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AA2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="AB2" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="AC2" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -1404,46 +1452,46 @@
         <v>3</v>
       </c>
       <c r="BC2" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="BD2">
         <v>21</v>
       </c>
       <c r="BE2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="BF2">
         <v>1651</v>
       </c>
       <c r="BG2" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="BH2">
         <v>7</v>
       </c>
       <c r="BI2" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="BJ2" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="BK2" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="BL2">
         <v>23850969</v>
       </c>
       <c r="BM2" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="BN2" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="BO2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="BP2" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="BQ2">
         <v>11</v>
@@ -1452,25 +1500,25 @@
         <v>2</v>
       </c>
       <c r="BS2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="BT2">
         <v>2371</v>
       </c>
       <c r="BU2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="BV2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="BW2">
         <v>36000</v>
       </c>
       <c r="BX2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="BY2" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="BZ2">
         <v>2026</v>
@@ -1479,19 +1527,19 @@
         <v>50</v>
       </c>
       <c r="CB2" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="CC2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="CD2" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="CE2" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="DE2" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="DF2">
         <v>0</v>
@@ -1499,121 +1547,130 @@
     </row>
     <row r="3" spans="1:110">
       <c r="A3">
-        <v>1365200</v>
+        <v>1692954</v>
       </c>
       <c r="B3" t="s">
         <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F3">
-        <v>543464559391</v>
+        <v>5493835518006</v>
       </c>
       <c r="G3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I3">
-        <v>378</v>
+        <v>336</v>
       </c>
       <c r="J3" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K3">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="M3">
         <v>18</v>
       </c>
-      <c r="S3" t="s">
-        <v>140</v>
-      </c>
       <c r="T3" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="U3" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="V3" t="s">
+        <v>152</v>
+      </c>
+      <c r="W3" t="s">
+        <v>156</v>
+      </c>
+      <c r="X3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>159</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>121</v>
+      </c>
+      <c r="AB3" t="s">
         <v>146</v>
       </c>
-      <c r="W3" t="s">
-        <v>149</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>151</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>119</v>
+      <c r="AC3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
       </c>
       <c r="BB3">
         <v>1</v>
       </c>
       <c r="BC3" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="BD3">
         <v>24</v>
       </c>
       <c r="BE3" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="BF3">
-        <v>983</v>
+        <v>1050</v>
       </c>
       <c r="BG3" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="BH3">
         <v>1</v>
       </c>
       <c r="BI3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="BJ3" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="BK3" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="BL3">
-        <v>23012881</v>
+        <v>43218584</v>
       </c>
       <c r="BM3" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="BN3" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="BO3" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="BP3" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="BQ3">
         <v>1</v>
       </c>
       <c r="BV3" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="BW3">
         <v>56500</v>
       </c>
       <c r="BX3" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="BY3" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="BZ3">
         <v>2026</v>
@@ -1622,19 +1679,19 @@
         <v>50</v>
       </c>
       <c r="CB3" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="CC3" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="CD3" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="CE3" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="DE3" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="DF3">
         <v>0</v>
@@ -1642,130 +1699,121 @@
     </row>
     <row r="4" spans="1:110">
       <c r="A4">
-        <v>1385414</v>
+        <v>1365200</v>
       </c>
       <c r="B4" t="s">
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E4">
-        <v>40992434</v>
+        <v>122</v>
       </c>
       <c r="F4">
-        <v>543442305585</v>
+        <v>543464559391</v>
       </c>
       <c r="G4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="H4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I4">
-        <v>9</v>
+        <v>378</v>
       </c>
       <c r="J4" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="K4">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L4" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="M4">
-        <v>103</v>
-      </c>
-      <c r="N4" t="s">
-        <v>133</v>
-      </c>
-      <c r="O4" t="s">
-        <v>135</v>
-      </c>
-      <c r="P4" t="s">
-        <v>137</v>
+        <v>18</v>
+      </c>
+      <c r="S4" t="s">
+        <v>146</v>
       </c>
       <c r="T4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="U4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="V4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="W4" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="Y4" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AA4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="BB4">
         <v>1</v>
       </c>
       <c r="BC4" t="s">
-        <v>157</v>
+        <v>135</v>
       </c>
       <c r="BD4">
         <v>24</v>
       </c>
       <c r="BE4" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="BF4">
-        <v>1050</v>
+        <v>983</v>
       </c>
       <c r="BG4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="BH4">
         <v>1</v>
       </c>
       <c r="BI4" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="BJ4" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="BK4" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="BL4">
-        <v>45181896</v>
+        <v>23012881</v>
       </c>
       <c r="BM4" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="BN4" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="BO4" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="BP4" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="BQ4">
         <v>1</v>
       </c>
       <c r="BV4" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="BW4">
         <v>56500</v>
       </c>
       <c r="BX4" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="BY4" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="BZ4">
         <v>2026</v>
@@ -1774,19 +1822,19 @@
         <v>50</v>
       </c>
       <c r="CB4" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="CC4" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="CD4" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="CE4" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="DE4" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="DF4">
         <v>0</v>
@@ -1794,145 +1842,130 @@
     </row>
     <row r="5" spans="1:110">
       <c r="A5">
-        <v>1663213</v>
+        <v>1385414</v>
       </c>
       <c r="B5" t="s">
         <v>113</v>
       </c>
       <c r="C5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="E5">
+        <v>40992434</v>
       </c>
       <c r="F5">
-        <v>5493873256079</v>
+        <v>543442305585</v>
       </c>
       <c r="G5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H5" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="I5">
-        <v>113</v>
+        <v>9</v>
       </c>
       <c r="J5" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K5">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="L5" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="M5">
-        <v>297</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="O5" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="P5" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>139</v>
-      </c>
-      <c r="R5">
-        <v>551860803098</v>
+        <v>143</v>
+      </c>
+      <c r="T5" t="s">
+        <v>147</v>
       </c>
       <c r="U5" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="V5" t="s">
-        <v>148</v>
+        <v>154</v>
+      </c>
+      <c r="W5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>159</v>
       </c>
       <c r="AA5" t="s">
-        <v>152</v>
-      </c>
-      <c r="AB5" t="s">
-        <v>140</v>
-      </c>
-      <c r="AC5" t="s">
-        <v>155</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="BB5">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BC5" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="BD5">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="BE5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="BF5">
-        <v>1716</v>
+        <v>1050</v>
       </c>
       <c r="BG5" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="BH5">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BI5" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="BJ5" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="BK5" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="BL5">
-        <v>36266314</v>
+        <v>45181896</v>
       </c>
       <c r="BM5" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="BN5" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="BO5" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="BP5" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="BQ5">
-        <v>11</v>
-      </c>
-      <c r="BR5">
-        <v>3</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>183</v>
-      </c>
-      <c r="BT5">
-        <v>2411</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>185</v>
+        <v>1</v>
       </c>
       <c r="BV5" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="BW5">
-        <v>75000</v>
+        <v>56500</v>
       </c>
       <c r="BX5" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="BY5" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="BZ5">
         <v>2026</v>
@@ -1941,21 +1974,188 @@
         <v>50</v>
       </c>
       <c r="CB5" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="CC5" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="CD5" t="s">
-        <v>121</v>
+        <v>219</v>
       </c>
       <c r="CE5" t="s">
+        <v>221</v>
+      </c>
+      <c r="DE5" t="s">
+        <v>223</v>
+      </c>
+      <c r="DF5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:110">
+      <c r="A6">
+        <v>1663213</v>
+      </c>
+      <c r="B6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" t="s">
+        <v>119</v>
+      </c>
+      <c r="D6" t="s">
+        <v>124</v>
+      </c>
+      <c r="F6">
+        <v>5493873256079</v>
+      </c>
+      <c r="G6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H6" t="s">
+        <v>127</v>
+      </c>
+      <c r="I6">
+        <v>113</v>
+      </c>
+      <c r="J6" t="s">
+        <v>133</v>
+      </c>
+      <c r="K6">
+        <v>9</v>
+      </c>
+      <c r="L6" t="s">
+        <v>138</v>
+      </c>
+      <c r="M6">
+        <v>297</v>
+      </c>
+      <c r="N6" t="s">
+        <v>140</v>
+      </c>
+      <c r="O6" t="s">
+        <v>142</v>
+      </c>
+      <c r="P6" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>145</v>
+      </c>
+      <c r="R6">
+        <v>551860803098</v>
+      </c>
+      <c r="U6" t="s">
+        <v>149</v>
+      </c>
+      <c r="V6" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>160</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>146</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>164</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="BB6">
+        <v>3</v>
+      </c>
+      <c r="BC6" t="s">
+        <v>165</v>
+      </c>
+      <c r="BD6">
+        <v>9</v>
+      </c>
+      <c r="BE6" t="s">
+        <v>168</v>
+      </c>
+      <c r="BF6">
+        <v>1716</v>
+      </c>
+      <c r="BG6" t="s">
+        <v>172</v>
+      </c>
+      <c r="BH6">
+        <v>7</v>
+      </c>
+      <c r="BI6" t="s">
+        <v>173</v>
+      </c>
+      <c r="BJ6" t="s">
+        <v>175</v>
+      </c>
+      <c r="BK6" t="s">
+        <v>176</v>
+      </c>
+      <c r="BL6">
+        <v>36266314</v>
+      </c>
+      <c r="BM6" t="s">
+        <v>181</v>
+      </c>
+      <c r="BN6" t="s">
+        <v>186</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>189</v>
+      </c>
+      <c r="BP6" t="s">
+        <v>193</v>
+      </c>
+      <c r="BQ6">
+        <v>11</v>
+      </c>
+      <c r="BR6">
+        <v>3</v>
+      </c>
+      <c r="BS6" t="s">
+        <v>195</v>
+      </c>
+      <c r="BT6">
+        <v>2411</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>197</v>
+      </c>
+      <c r="BV6" t="s">
+        <v>198</v>
+      </c>
+      <c r="BW6">
+        <v>75000</v>
+      </c>
+      <c r="BX6" t="s">
+        <v>201</v>
+      </c>
+      <c r="BY6" t="s">
         <v>205</v>
       </c>
-      <c r="DE5" t="s">
-        <v>207</v>
-      </c>
-      <c r="DF5">
+      <c r="BZ6">
+        <v>2026</v>
+      </c>
+      <c r="CA6">
+        <v>50</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>210</v>
+      </c>
+      <c r="CC6" t="s">
+        <v>215</v>
+      </c>
+      <c r="CD6" t="s">
+        <v>124</v>
+      </c>
+      <c r="CE6" t="s">
+        <v>221</v>
+      </c>
+      <c r="DE6" t="s">
+        <v>223</v>
+      </c>
+      <c r="DF6">
         <v>0</v>
       </c>
     </row>
